--- a/DateBase/orders/Nha Thu_2026-4-21.xlsx
+++ b/DateBase/orders/Nha Thu_2026-4-21.xlsx
@@ -1017,6 +1017,9 @@
       <c r="G2" t="str">
         <v>010101015510155200252020105201520101015151015515610615136511051060100981051515555102051071010105510102010</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
